--- a/job_application_forms/036_visual_communication_expert_hiring_application--job_application_forms.xlsx
+++ b/job_application_forms/036_visual_communication_expert_hiring_application--job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>behance</t>
+          <t>flickr</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Behance</t>
+          <t>Flickr</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>flickr</t>
+          <t>deviantart</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Flickr</t>
+          <t>DeviantArt</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>deviantart</t>
+          <t>500px</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DeviantArt</t>
+          <t>500px</t>
         </is>
       </c>
     </row>
@@ -899,29 +899,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>500px</t>
+          <t>dropbox</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>500px</t>
+          <t>Dropbox</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>portfolio_choices</t>
+          <t>skills_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>dropbox</t>
+          <t>visual_design</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Visual Design</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>visual_design</t>
+          <t>ui/ux_design</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Visual Design</t>
+          <t>UI/UX Design</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ui/ux_design</t>
+          <t>web_design</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UI/UX Design</t>
+          <t>Web Design</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>web_design</t>
+          <t>graphic_design</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Web Design</t>
+          <t>Graphic Design</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>graphic_design</t>
+          <t>illustration</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Graphic Design</t>
+          <t>Illustration</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>illustration</t>
+          <t>animation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Illustration</t>
+          <t>Animation</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>animation</t>
+          <t>motion_graphics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Animation</t>
+          <t>Motion Graphics</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>motion_graphics</t>
+          <t>photography</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Motion Graphics</t>
+          <t>Photography</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>photography</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Photography</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -1069,29 +1069,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>3d_modeling</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>3D Modeling</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>portfolio_links_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3d_modeling</t>
+          <t>website_url</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3D Modeling</t>
+          <t>Website URL</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>website_url</t>
+          <t>behance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Website URL</t>
+          <t>Behance</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>behance</t>
+          <t>dribbble</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Behance</t>
+          <t>Dribbble</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>dribbble</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dribbble</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>LinkedIn</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>deviantart</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>DeviantArt</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>deviantart</t>
+          <t>flickr</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DeviantArt</t>
+          <t>Flickr</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>flickr</t>
+          <t>500px</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Flickr</t>
+          <t>500px</t>
         </is>
       </c>
     </row>
@@ -1222,27 +1222,10 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>500px</t>
+          <t>dropbox</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
-        <is>
-          <t>500px</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>portfolio_links_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>dropbox</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
         <is>
           <t>Dropbox</t>
         </is>
